--- a/573230_Hirako_Megumi.xlsx
+++ b/573230_Hirako_Megumi.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="明細" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="説明別合計" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2025-09-30" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2025-12-31" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-03-31" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,17 +29,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,11 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,18 +83,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +461,7 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -484,204 +478,125 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Hirako, Megumi（コード:573230）  Investment Mgmt Fee for 30/09/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>イントロデューサーコード</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>イントロデューサー氏名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>プラン番号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>シーケンス</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>商品コード</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>期間</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>通貨</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>イントロデューサー0.5%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr"/>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>573230</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Hirako, Megumi</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>T25W030638</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>基本プラン</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Doi, Yuusaku</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Investment Mgmt Fee for 30/09/2025</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>EVO25</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>12.38</v>
       </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>573230</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Hirako, Megumi</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>T25W030638</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>基本プラン</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Doi, Yuusaku</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Investment Mgmt Fee for 31/12/2025</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>EVO25</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>573230</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Hirako, Megumi</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>T25W030638</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>基本プラン</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Doi, Yuusaku</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Investment Mgmt Fee for 31/03/2026</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>EVO25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>12.38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -694,97 +609,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Hirako, Megumi（コード:573230） 説明別 合計金額（イントロデューサー0.5%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hirako, Megumi（コード:573230）  Investment Mgmt Fee for 31/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>イントロデューサーコード</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>イントロデューサー氏名</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>プラン番号</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>シーケンス</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>商品コード</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>通貨</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>イントロデューサー0.5%</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>F列 説明</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>合計金額</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="n">
+        <v>573230</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Hirako, Megumi</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>T25W030638</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>基本プラン</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Doi, Yuusaku</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Investment Mgmt Fee for 31/12/2025</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>EVO25</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>14.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hirako, Megumi（コード:573230）  Investment Mgmt Fee for 31/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>イントロデューサーコード</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>イントロデューサー氏名</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>プラン番号</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>シーケンス</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>商品コード</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>通貨</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>イントロデューサー0.5%</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>573230</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Hirako, Megumi</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>T25W030638</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>基本プラン</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Doi, Yuusaku</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Investment Mgmt Fee for 31/03/2026</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>EVO25</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Investment Mgmt Fee for 30/09/2025</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Investment Mgmt Fee for 31/12/2025</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Investment Mgmt Fee for 31/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>15.35</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>総合計</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>41.97</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
       </c>
     </row>
   </sheetData>
